--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2301-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2301-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6A84F1D-E206-4155-89E3-A9091B0B8B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFEEBEB3-B75E-4C37-95CD-A39A1CD84F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{2A7A59B2-1259-4BBE-9AAD-729BA2127C88}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{B25B043E-CF86-4AA3-B645-530FCD94B8F4}"/>
   </bookViews>
   <sheets>
     <sheet name="2301-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1532,25 +1532,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB58381-5F54-409F-A41D-92FB031A6B27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95E24DE-6149-4C78-9F68-B1A6A1E7ACC8}">
   <dimension ref="A1:R66"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1578,7 +1578,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1608,7 +1608,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1704,7 +1704,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2020</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>25</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2019</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>25</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>25</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2018</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2017</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2016</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2015</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2014</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2013</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2012</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2011</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2010</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>2009</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>2008</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>2007</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>2006</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>2005</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>2004</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
         <v>2003</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>2002</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="37">
         <v>2001</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="39">
         <v>2000</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="37">
         <v>1999</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="39">
         <v>1998</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>1997</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="39">
         <v>1996</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="37">
         <v>1995</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="39">
         <v>1994</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="37">
         <v>1993</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="39" t="s">
         <v>63</v>
       </c>
